--- a/docs/wordlist-patch.xlsx
+++ b/docs/wordlist-patch.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C105"/>
+  <dimension ref="A1:C107"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -415,7 +415,7 @@
         <v/>
       </c>
       <c r="B2" t="str">
-        <v>(Demo) Tap to advance the demo.</v>
+        <v>— select members below</v>
       </c>
       <c r="C2" t="str">
         <v/>
@@ -426,7 +426,7 @@
         <v/>
       </c>
       <c r="B3" t="str">
-        <v>11:59 PM (before City Selection opens)</v>
+        <v>(Demo) Tap to advance the demo.</v>
       </c>
       <c r="C3" t="str">
         <v/>
@@ -437,7 +437,7 @@
         <v/>
       </c>
       <c r="B4" t="str">
-        <v>3 family members</v>
+        <v>11:59 PM (before City Selection opens)</v>
       </c>
       <c r="C4" t="str">
         <v/>
@@ -448,7 +448,7 @@
         <v/>
       </c>
       <c r="B5" t="str">
-        <v>4.0 MB</v>
+        <v>3 family members</v>
       </c>
       <c r="C5" t="str">
         <v/>
@@ -459,7 +459,7 @@
         <v/>
       </c>
       <c r="B6" t="str">
-        <v>Abu Dhabi</v>
+        <v>4.0 MB</v>
       </c>
       <c r="C6" t="str">
         <v/>
@@ -470,7 +470,7 @@
         <v/>
       </c>
       <c r="B7" t="str">
-        <v>Action</v>
+        <v>Abu Dhabi</v>
       </c>
       <c r="C7" t="str">
         <v/>
@@ -481,7 +481,7 @@
         <v/>
       </c>
       <c r="B8" t="str">
-        <v>Admin registered on your behalf</v>
+        <v>Action</v>
       </c>
       <c r="C8" t="str">
         <v/>
@@ -492,7 +492,7 @@
         <v/>
       </c>
       <c r="B9" t="str">
-        <v>Ajman</v>
+        <v>added</v>
       </c>
       <c r="C9" t="str">
         <v/>
@@ -503,7 +503,7 @@
         <v/>
       </c>
       <c r="B10" t="str">
-        <v>Al Ain</v>
+        <v>Admin registered on your behalf</v>
       </c>
       <c r="C10" t="str">
         <v/>
@@ -514,7 +514,7 @@
         <v/>
       </c>
       <c r="B11" t="str">
-        <v>All</v>
+        <v>Ajman</v>
       </c>
       <c r="C11" t="str">
         <v/>
@@ -525,7 +525,7 @@
         <v/>
       </c>
       <c r="B12" t="str">
-        <v>Allocate</v>
+        <v>Al Ain</v>
       </c>
       <c r="C12" t="str">
         <v/>
@@ -536,7 +536,7 @@
         <v/>
       </c>
       <c r="B13" t="str">
-        <v>Allocation</v>
+        <v>All</v>
       </c>
       <c r="C13" t="str">
         <v/>
@@ -547,7 +547,7 @@
         <v/>
       </c>
       <c r="B14" t="str">
-        <v>An Idaratul Miqaat admin registered you for Eid-e-Ghadeer 1447H.</v>
+        <v>Allocate</v>
       </c>
       <c r="C14" t="str">
         <v/>
@@ -558,7 +558,7 @@
         <v/>
       </c>
       <c r="B15" t="str">
-        <v>Araz · Preferred City</v>
+        <v>Allocation</v>
       </c>
       <c r="C15" t="str">
         <v/>
@@ -569,7 +569,7 @@
         <v/>
       </c>
       <c r="B16" t="str">
-        <v>Berlin</v>
+        <v>An Idaratul Miqaat admin registered you for Eid-e-Ghadeer 1447H.</v>
       </c>
       <c r="C16" t="str">
         <v/>
@@ -580,7 +580,7 @@
         <v/>
       </c>
       <c r="B17" t="str">
-        <v>Birmingham</v>
+        <v>Araz · Preferred City</v>
       </c>
       <c r="C17" t="str">
         <v/>
@@ -591,7 +591,7 @@
         <v/>
       </c>
       <c r="B18" t="str">
-        <v>CURRENT</v>
+        <v>Berlin</v>
       </c>
       <c r="C18" t="str">
         <v/>
@@ -602,7 +602,7 @@
         <v/>
       </c>
       <c r="B19" t="str">
-        <v>Calgary</v>
+        <v>Birmingham</v>
       </c>
       <c r="C19" t="str">
         <v/>
@@ -613,7 +613,7 @@
         <v/>
       </c>
       <c r="B20" t="str">
-        <v>Change Relay City</v>
+        <v>Calgary</v>
       </c>
       <c r="C20" t="str">
         <v/>
@@ -624,7 +624,7 @@
         <v/>
       </c>
       <c r="B21" t="str">
-        <v>Chicago</v>
+        <v>Change Relay City</v>
       </c>
       <c r="C21" t="str">
         <v/>
@@ -635,7 +635,7 @@
         <v/>
       </c>
       <c r="B22" t="str">
-        <v>Choose city</v>
+        <v>Chicago</v>
       </c>
       <c r="C22" t="str">
         <v/>
@@ -646,7 +646,7 @@
         <v/>
       </c>
       <c r="B23" t="str">
-        <v>Choose the Host City radio for each member in the table below.</v>
+        <v>Choose city</v>
       </c>
       <c r="C23" t="str">
         <v/>
@@ -657,7 +657,7 @@
         <v/>
       </c>
       <c r="B24" t="str">
-        <v>Choose the Host City radio for each member in the table.</v>
+        <v>Choose the Host City radio for each member in the table below.</v>
       </c>
       <c r="C24" t="str">
         <v/>
@@ -668,7 +668,7 @@
         <v/>
       </c>
       <c r="B25" t="str">
-        <v>Choose the Relay City radio, then pick a city from the dropdown for each member.</v>
+        <v>Choose the Host City radio for each member in the table.</v>
       </c>
       <c r="C25" t="str">
         <v/>
@@ -690,7 +690,7 @@
         <v/>
       </c>
       <c r="B27" t="str">
-        <v>City arrangement</v>
+        <v>Choose the Relay City radio, then pick a city from the dropdown for each member.</v>
       </c>
       <c r="C27" t="str">
         <v/>
@@ -701,7 +701,7 @@
         <v/>
       </c>
       <c r="B28" t="str">
-        <v>City selection has closed.</v>
+        <v>city</v>
       </c>
       <c r="C28" t="str">
         <v/>
@@ -712,7 +712,7 @@
         <v/>
       </c>
       <c r="B29" t="str">
-        <v>Close in 00:42:11</v>
+        <v>City arrangement</v>
       </c>
       <c r="C29" t="str">
         <v/>
@@ -723,7 +723,7 @@
         <v/>
       </c>
       <c r="B30" t="str">
-        <v>Cologne</v>
+        <v>City selection has closed.</v>
       </c>
       <c r="C30" t="str">
         <v/>
@@ -734,7 +734,7 @@
         <v/>
       </c>
       <c r="B31" t="str">
-        <v>Frankfurt</v>
+        <v>Close in 00:42:11</v>
       </c>
       <c r="C31" t="str">
         <v/>
@@ -745,7 +745,7 @@
         <v/>
       </c>
       <c r="B32" t="str">
-        <v>Glasgow</v>
+        <v>Cologne</v>
       </c>
       <c r="C32" t="str">
         <v/>
@@ -756,7 +756,7 @@
         <v/>
       </c>
       <c r="B33" t="str">
-        <v>Headcount</v>
+        <v>CURRENT</v>
       </c>
       <c r="C33" t="str">
         <v/>
@@ -767,7 +767,7 @@
         <v/>
       </c>
       <c r="B34" t="str">
-        <v>Host city</v>
+        <v>Frankfurt</v>
       </c>
       <c r="C34" t="str">
         <v/>
@@ -778,7 +778,7 @@
         <v/>
       </c>
       <c r="B35" t="str">
-        <v>Houston</v>
+        <v>Glasgow</v>
       </c>
       <c r="C35" t="str">
         <v/>
@@ -789,7 +789,7 @@
         <v/>
       </c>
       <c r="B36" t="str">
-        <v>Invitation</v>
+        <v>Headcount</v>
       </c>
       <c r="C36" t="str">
         <v/>
@@ -800,7 +800,7 @@
         <v/>
       </c>
       <c r="B37" t="str">
-        <v>Invited Mehmaan stay</v>
+        <v>‏Home</v>
       </c>
       <c r="C37" t="str">
         <v/>
@@ -811,7 +811,7 @@
         <v/>
       </c>
       <c r="B38" t="str">
-        <v>Leeds</v>
+        <v>host</v>
       </c>
       <c r="C38" t="str">
         <v/>
@@ -822,7 +822,7 @@
         <v/>
       </c>
       <c r="B39" t="str">
-        <v>Liverpool</v>
+        <v>Host city</v>
       </c>
       <c r="C39" t="str">
         <v/>
@@ -833,7 +833,7 @@
         <v/>
       </c>
       <c r="B40" t="str">
-        <v>Los angels</v>
+        <v>Houston</v>
       </c>
       <c r="C40" t="str">
         <v/>
@@ -844,7 +844,7 @@
         <v/>
       </c>
       <c r="B41" t="str">
-        <v>Manchester</v>
+        <v>Invitation</v>
       </c>
       <c r="C41" t="str">
         <v/>
@@ -855,7 +855,7 @@
         <v/>
       </c>
       <c r="B42" t="str">
-        <v>Max</v>
+        <v>Invited Mehmaan stay</v>
       </c>
       <c r="C42" t="str">
         <v/>
@@ -866,7 +866,7 @@
         <v/>
       </c>
       <c r="B43" t="str">
-        <v>Miami</v>
+        <v>Leeds</v>
       </c>
       <c r="C43" t="str">
         <v/>
@@ -877,7 +877,7 @@
         <v/>
       </c>
       <c r="B44" t="str">
-        <v>Montreal</v>
+        <v>Liverpool</v>
       </c>
       <c r="C44" t="str">
         <v/>
@@ -888,7 +888,7 @@
         <v/>
       </c>
       <c r="B45" t="str">
-        <v>Move to Colombo</v>
+        <v>Los angels</v>
       </c>
       <c r="C45" t="str">
         <v/>
@@ -899,7 +899,7 @@
         <v/>
       </c>
       <c r="B46" t="str">
-        <v>Munich</v>
+        <v>Manchester</v>
       </c>
       <c r="C46" t="str">
         <v/>
@@ -910,7 +910,7 @@
         <v/>
       </c>
       <c r="B47" t="str">
-        <v>Murtaza bhai Moiz bhai Gheewala has been assigned as your guardian. Please accept the request to continue.</v>
+        <v>Max</v>
       </c>
       <c r="C47" t="str">
         <v/>
@@ -921,7 +921,7 @@
         <v/>
       </c>
       <c r="B48" t="str">
-        <v>Murtaza bhai Moiz bhai Gheewala has invited you to join their group</v>
+        <v>members</v>
       </c>
       <c r="C48" t="str">
         <v/>
@@ -932,7 +932,7 @@
         <v/>
       </c>
       <c r="B49" t="str">
-        <v>My family</v>
+        <v>members below</v>
       </c>
       <c r="C49" t="str">
         <v/>
@@ -943,7 +943,7 @@
         <v/>
       </c>
       <c r="B50" t="str">
-        <v>New york</v>
+        <v>Miami</v>
       </c>
       <c r="C50" t="str">
         <v/>
@@ -954,7 +954,7 @@
         <v/>
       </c>
       <c r="B51" t="str">
-        <v>None selected</v>
+        <v>Montreal</v>
       </c>
       <c r="C51" t="str">
         <v/>
@@ -965,7 +965,7 @@
         <v/>
       </c>
       <c r="B52" t="str">
-        <v>Not confirmed</v>
+        <v>Move to Colombo</v>
       </c>
       <c r="C52" t="str">
         <v/>
@@ -976,7 +976,7 @@
         <v/>
       </c>
       <c r="B53" t="str">
-        <v>Other Cities (</v>
+        <v>Munich</v>
       </c>
       <c r="C53" t="str">
         <v/>
@@ -987,7 +987,7 @@
         <v/>
       </c>
       <c r="B54" t="str">
-        <v>Ottawa</v>
+        <v>Murtaza bhai Moiz bhai Gheewala has been assigned as your guardian. Please accept the request to continue.</v>
       </c>
       <c r="C54" t="str">
         <v/>
@@ -998,7 +998,7 @@
         <v/>
       </c>
       <c r="B55" t="str">
-        <v>PDF · 248 KB</v>
+        <v>Murtaza bhai Moiz bhai Gheewala has invited you to join their group</v>
       </c>
       <c r="C55" t="str">
         <v/>
@@ -1009,7 +1009,7 @@
         <v/>
       </c>
       <c r="B56" t="str">
-        <v>People in your reservation</v>
+        <v>My family</v>
       </c>
       <c r="C56" t="str">
         <v/>
@@ -1020,7 +1020,7 @@
         <v/>
       </c>
       <c r="B57" t="str">
-        <v>Raza Pending</v>
+        <v>New york</v>
       </c>
       <c r="C57" t="str">
         <v/>
@@ -1031,7 +1031,7 @@
         <v/>
       </c>
       <c r="B58" t="str">
-        <v>Raza Status</v>
+        <v>None selected</v>
       </c>
       <c r="C58" t="str">
         <v/>
@@ -1042,7 +1042,7 @@
         <v/>
       </c>
       <c r="B59" t="str">
-        <v>Raza has not been issued yet for your group.</v>
+        <v>Not confirmed</v>
       </c>
       <c r="C59" t="str">
         <v/>
@@ -1053,7 +1053,7 @@
         <v/>
       </c>
       <c r="B60" t="str">
-        <v>Raza letter — Eid-e-Ghadeer 1447H</v>
+        <v>Other Cities (</v>
       </c>
       <c r="C60" t="str">
         <v/>
@@ -1064,7 +1064,7 @@
         <v/>
       </c>
       <c r="B61" t="str">
-        <v>Reach out to your Miqaat coordinator if something here needs correcting.</v>
+        <v>Ottawa</v>
       </c>
       <c r="C61" t="str">
         <v/>
@@ -1075,7 +1075,7 @@
         <v/>
       </c>
       <c r="B62" t="str">
-        <v>Ready for Registration</v>
+        <v>PDF · 248 KB</v>
       </c>
       <c r="C62" t="str">
         <v/>
@@ -1086,7 +1086,7 @@
         <v/>
       </c>
       <c r="B63" t="str">
-        <v>Registration opens in {date}</v>
+        <v>People in your reservation</v>
       </c>
       <c r="C63" t="str">
         <v/>
@@ -1097,7 +1097,7 @@
         <v/>
       </c>
       <c r="B64" t="str">
-        <v>Request</v>
+        <v>Raza has not been issued yet for your group.</v>
       </c>
       <c r="C64" t="str">
         <v/>
@@ -1108,7 +1108,7 @@
         <v/>
       </c>
       <c r="B65" t="str">
-        <v>Request all</v>
+        <v>Raza letter — Eid-e-Ghadeer 1447H</v>
       </c>
       <c r="C65" t="str">
         <v/>
@@ -1119,7 +1119,7 @@
         <v/>
       </c>
       <c r="B66" t="str">
-        <v>Request received</v>
+        <v>Raza Pending</v>
       </c>
       <c r="C66" t="str">
         <v/>
@@ -1130,7 +1130,7 @@
         <v/>
       </c>
       <c r="B67" t="str">
-        <v>Request to</v>
+        <v>Raza Status</v>
       </c>
       <c r="C67" t="str">
         <v/>
@@ -1141,7 +1141,7 @@
         <v/>
       </c>
       <c r="B68" t="str">
-        <v>Requests</v>
+        <v>Reach out to your Miqaat coordinator if something here needs correcting.</v>
       </c>
       <c r="C68" t="str">
         <v/>
@@ -1152,7 +1152,7 @@
         <v/>
       </c>
       <c r="B69" t="str">
-        <v>San Francisco</v>
+        <v>Ready for Registration</v>
       </c>
       <c r="C69" t="str">
         <v/>
@@ -1163,7 +1163,7 @@
         <v/>
       </c>
       <c r="B70" t="str">
-        <v>Sat, 21 Jun, 2026</v>
+        <v>‏Registered</v>
       </c>
       <c r="C70" t="str">
         <v/>
@@ -1174,7 +1174,7 @@
         <v/>
       </c>
       <c r="B71" t="str">
-        <v>Save Preferences</v>
+        <v>Registration opens in {date}</v>
       </c>
       <c r="C71" t="str">
         <v/>
@@ -1185,7 +1185,7 @@
         <v/>
       </c>
       <c r="B72" t="str">
-        <v>Seattle</v>
+        <v>relay</v>
       </c>
       <c r="C72" t="str">
         <v/>
@@ -1196,7 +1196,7 @@
         <v/>
       </c>
       <c r="B73" t="str">
-        <v>Sharjah</v>
+        <v>request</v>
       </c>
       <c r="C73" t="str">
         <v/>
@@ -1207,7 +1207,7 @@
         <v/>
       </c>
       <c r="B74" t="str">
-        <v>Slot</v>
+        <v>Request</v>
       </c>
       <c r="C74" t="str">
         <v/>
@@ -1218,7 +1218,7 @@
         <v/>
       </c>
       <c r="B75" t="str">
-        <v>Slot reminder</v>
+        <v>Request all</v>
       </c>
       <c r="C75" t="str">
         <v/>
@@ -1229,7 +1229,7 @@
         <v/>
       </c>
       <c r="B76" t="str">
-        <v>Stuttgart</v>
+        <v>Request received</v>
       </c>
       <c r="C76" t="str">
         <v/>
@@ -1240,7 +1240,7 @@
         <v/>
       </c>
       <c r="B77" t="str">
-        <v>Submit for approval</v>
+        <v>Request to</v>
       </c>
       <c r="C77" t="str">
         <v/>
@@ -1251,7 +1251,7 @@
         <v/>
       </c>
       <c r="B78" t="str">
-        <v>Submit request</v>
+        <v>Requests</v>
       </c>
       <c r="C78" t="str">
         <v/>
@@ -1262,7 +1262,7 @@
         <v/>
       </c>
       <c r="B79" t="str">
-        <v>Submit your preferences</v>
+        <v>San Francisco</v>
       </c>
       <c r="C79" t="str">
         <v/>
@@ -1273,7 +1273,7 @@
         <v/>
       </c>
       <c r="B80" t="str">
-        <v>Switch to Colombo</v>
+        <v>Sat, 21 Jun, 2026</v>
       </c>
       <c r="C80" t="str">
         <v/>
@@ -1284,7 +1284,7 @@
         <v/>
       </c>
       <c r="B81" t="str">
-        <v>System</v>
+        <v>Save Preferences</v>
       </c>
       <c r="C81" t="str">
         <v/>
@@ -1295,7 +1295,7 @@
         <v/>
       </c>
       <c r="B82" t="str">
-        <v>The complete journey at a glance — registration, city and zone selection, Raza, and the day of Miqaat.</v>
+        <v>Seattle</v>
       </c>
       <c r="C82" t="str">
         <v/>
@@ -1306,7 +1306,7 @@
         <v/>
       </c>
       <c r="B83" t="str">
-        <v>This Miqaat can no longer be registered for.</v>
+        <v>Sharjah</v>
       </c>
       <c r="C83" t="str">
         <v/>
@@ -1317,7 +1317,7 @@
         <v/>
       </c>
       <c r="B84" t="str">
-        <v>Total</v>
+        <v>Slot</v>
       </c>
       <c r="C84" t="str">
         <v/>
@@ -1328,7 +1328,7 @@
         <v/>
       </c>
       <c r="B85" t="str">
-        <v>United Arab Emirates</v>
+        <v>Slot reminder</v>
       </c>
       <c r="C85" t="str">
         <v/>
@@ -1339,7 +1339,7 @@
         <v/>
       </c>
       <c r="B86" t="str">
-        <v>Vancouver</v>
+        <v>starts</v>
       </c>
       <c r="C86" t="str">
         <v/>
@@ -1350,7 +1350,7 @@
         <v/>
       </c>
       <c r="B87" t="str">
-        <v>You're all set</v>
+        <v>Stuttgart</v>
       </c>
       <c r="C87" t="str">
         <v/>
@@ -1361,7 +1361,7 @@
         <v/>
       </c>
       <c r="B88" t="str">
-        <v>Your Phase 1 city selection slot opens in 1 hour. Be ready to pick your city.</v>
+        <v>Submit for approval</v>
       </c>
       <c r="C88" t="str">
         <v/>
@@ -1372,7 +1372,7 @@
         <v/>
       </c>
       <c r="B89" t="str">
-        <v>Your family(</v>
+        <v>Submit request</v>
       </c>
       <c r="C89" t="str">
         <v/>
@@ -1383,7 +1383,7 @@
         <v/>
       </c>
       <c r="B90" t="str">
-        <v>Your members (</v>
+        <v>Submit your preferences</v>
       </c>
       <c r="C90" t="str">
         <v/>
@@ -1394,7 +1394,7 @@
         <v/>
       </c>
       <c r="B91" t="str">
-        <v>Your registered Miqaats that require your attention.</v>
+        <v>Switch to Colombo</v>
       </c>
       <c r="C91" t="str">
         <v/>
@@ -1405,7 +1405,7 @@
         <v/>
       </c>
       <c r="B92" t="str">
-        <v>Zone selection has closed.</v>
+        <v>System</v>
       </c>
       <c r="C92" t="str">
         <v/>
@@ -1416,7 +1416,7 @@
         <v/>
       </c>
       <c r="B93" t="str">
-        <v>added</v>
+        <v>terms and conditions</v>
       </c>
       <c r="C93" t="str">
         <v/>
@@ -1427,7 +1427,7 @@
         <v/>
       </c>
       <c r="B94" t="str">
-        <v>city</v>
+        <v>The complete journey at a glance — registration, city and zone selection, Raza, and the day of Miqaat.</v>
       </c>
       <c r="C94" t="str">
         <v/>
@@ -1438,7 +1438,7 @@
         <v/>
       </c>
       <c r="B95" t="str">
-        <v>host</v>
+        <v>This Miqaat can no longer be registered for.</v>
       </c>
       <c r="C95" t="str">
         <v/>
@@ -1449,7 +1449,7 @@
         <v/>
       </c>
       <c r="B96" t="str">
-        <v>members</v>
+        <v>Total</v>
       </c>
       <c r="C96" t="str">
         <v/>
@@ -1460,7 +1460,7 @@
         <v/>
       </c>
       <c r="B97" t="str">
-        <v>members below</v>
+        <v>United Arab Emirates</v>
       </c>
       <c r="C97" t="str">
         <v/>
@@ -1471,7 +1471,7 @@
         <v/>
       </c>
       <c r="B98" t="str">
-        <v>relay</v>
+        <v>until they accept their invitation. A seat is only used when each one accepts.</v>
       </c>
       <c r="C98" t="str">
         <v/>
@@ -1482,7 +1482,7 @@
         <v/>
       </c>
       <c r="B99" t="str">
-        <v>request</v>
+        <v>Vancouver</v>
       </c>
       <c r="C99" t="str">
         <v/>
@@ -1493,7 +1493,7 @@
         <v/>
       </c>
       <c r="B100" t="str">
-        <v>starts</v>
+        <v>What should your remarks be signed with?</v>
       </c>
       <c r="C100" t="str">
         <v/>
@@ -1504,7 +1504,7 @@
         <v/>
       </c>
       <c r="B101" t="str">
-        <v>terms and conditions</v>
+        <v>You're all set</v>
       </c>
       <c r="C101" t="str">
         <v/>
@@ -1515,7 +1515,7 @@
         <v/>
       </c>
       <c r="B102" t="str">
-        <v>until they accept their invitation. A seat is only used when each one accepts.</v>
+        <v>Your family(</v>
       </c>
       <c r="C102" t="str">
         <v/>
@@ -1526,7 +1526,7 @@
         <v/>
       </c>
       <c r="B103" t="str">
-        <v>‏Home</v>
+        <v>Your members (</v>
       </c>
       <c r="C103" t="str">
         <v/>
@@ -1537,7 +1537,7 @@
         <v/>
       </c>
       <c r="B104" t="str">
-        <v>‏Registered</v>
+        <v>Your name</v>
       </c>
       <c r="C104" t="str">
         <v/>
@@ -1548,15 +1548,37 @@
         <v/>
       </c>
       <c r="B105" t="str">
-        <v>— select members below</v>
+        <v>Your Phase 1 city selection slot opens in 1 hour. Be ready to pick your city.</v>
       </c>
       <c r="C105" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v/>
+      </c>
+      <c r="B106" t="str">
+        <v>Your registered Miqaats that require your attention.</v>
+      </c>
+      <c r="C106" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v/>
+      </c>
+      <c r="B107" t="str">
+        <v>Zone selection has closed.</v>
+      </c>
+      <c r="C107" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C105"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C107"/>
   </ignoredErrors>
 </worksheet>
 </file>